--- a/data/mk_fred_data_master.xlsx
+++ b/data/mk_fred_data_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5448,25 +5448,25 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3.668</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>3.667</v>
+        <v>3.668</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3.666</v>
+        <v>3.667</v>
       </c>
     </row>
     <row r="222">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5577,11 +5577,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>3.665</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="225">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>3.664</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="226">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>3.663</v>
+        <v>3.664</v>
       </c>
     </row>
     <row r="227">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3.662</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>3.661</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3.657</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3.655</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3.653</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>3.651</v>
+        <v>3.653</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>3.649</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3.644</v>
+        <v>3.649</v>
       </c>
     </row>
     <row r="236">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3.643</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="238">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>3.641</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>3.64</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="241">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>3.639</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="243">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3.638</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="245">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6083,57 +6083,57 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3.637</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1.24161826</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1.24199489</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1.24212012</v>
+        <v>1.24161826</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1.24224503</v>
+        <v>1.24199489</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1.2423696</v>
+        <v>1.24212012</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1.24249383</v>
+        <v>1.24224503</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1.24286658</v>
+        <v>1.2423696</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1.24299087</v>
+        <v>1.24249383</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1.24311517</v>
+        <v>1.24286658</v>
       </c>
     </row>
     <row r="256">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1.24323913</v>
+        <v>1.24299087</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1.24336207</v>
+        <v>1.24311517</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1.2437299</v>
+        <v>1.24323913</v>
       </c>
     </row>
     <row r="259">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1.24385186</v>
+        <v>1.24336207</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1.24397313</v>
+        <v>1.2437299</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1.24409407</v>
+        <v>1.24385186</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1.24421537</v>
+        <v>1.24397313</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1.24470615</v>
+        <v>1.24409407</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1.24483166</v>
+        <v>1.24421537</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1.24495718</v>
+        <v>1.24470615</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>1.24508236</v>
+        <v>1.24483166</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1.245459</v>
+        <v>1.24495718</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>1.24558528</v>
+        <v>1.24508236</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1.24571087</v>
+        <v>1.245459</v>
       </c>
     </row>
     <row r="270">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1.24583579</v>
+        <v>1.24558528</v>
       </c>
     </row>
     <row r="271">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1.24596107</v>
+        <v>1.24571087</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1.24633797</v>
+        <v>1.24583579</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1.24646364</v>
+        <v>1.24596107</v>
       </c>
     </row>
     <row r="274">
@@ -6727,80 +6727,80 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1.24658829</v>
+        <v>1.24633797</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4.97</v>
+        <v>1.24646364</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5.02</v>
+        <v>1.24658829</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4.98</v>
+        <v>1.2467126</v>
       </c>
     </row>
     <row r="278">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="282">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5.03</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="283">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="284">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5.02</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5.12</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5.14</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>5.03</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4.98</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>4.99</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4.99</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="297">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>5.01</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="301">
@@ -7348,10 +7348,79 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>13</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>US30Y</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>미국 국채 30년물 (CMT)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>13</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>US30Y</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>미국 국채 30년물 (CMT)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>13</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>US30Y</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>미국 국채 30년물 (CMT)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
           <t>20260609</t>
         </is>
       </c>
-      <c r="E301" t="n">
+      <c r="E304" t="n">
         <v>5.01</v>
       </c>
     </row>

--- a/data/mk_fred_data_master.xlsx
+++ b/data/mk_fred_data_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8367,6 +8367,1455 @@
         <v>4.97</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>14</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>20260501</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>14</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>20260504</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>14</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>20260505</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>14</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>20260506</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>14</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>20260507</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>14</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>14</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>14</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>14</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>20260513</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>14</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>14</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>14</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>14</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>14</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>14</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>14</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>14</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>20260526</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>14</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>20260527</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>14</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>14</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>14</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>14</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>14</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>14</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>14</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>14</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>14</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>14</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>14</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>14</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>14</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>US10Y_TIPS</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>미국 10년 실질금리 (TIPS)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>15</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>20260501</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>15</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>20260504</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>15</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>20260505</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>15</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>20260506</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>15</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>20260507</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>15</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>20260508</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>15</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>20260511</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>15</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>20260512</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>15</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>20260513</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>15</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>20260514</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>15</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>20260515</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>15</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>15</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>20260519</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>15</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>20260520</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>15</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>20260521</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>15</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>20260522</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>15</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>20260526</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>15</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>20260527</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>15</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>20260528</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>15</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>20260529</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>15</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>15</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>20260602</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>15</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>20260603</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>15</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>15</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>15</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>15</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>20260609</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>15</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>20260610</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>15</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>15</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>15</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>15</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>20260616</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mk_fred_data_master.xlsx
+++ b/data/mk_fred_data_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E408"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6184,25 +6184,25 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>3.668</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>3.667</v>
+        <v>3.668</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>3.666</v>
+        <v>3.667</v>
       </c>
     </row>
     <row r="254">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3.665</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3.664</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>3.663</v>
+        <v>3.664</v>
       </c>
     </row>
     <row r="259">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3.662</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3.661</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>3.657</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3.655</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>3.653</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3.651</v>
+        <v>3.653</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3.649</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3.644</v>
+        <v>3.649</v>
       </c>
     </row>
     <row r="268">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E268" t="n">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3.643</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="270">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3.641</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3.64</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="273">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>3.639</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="275">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3.638</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="277">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3.637</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="279">
@@ -6842,7 +6842,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="281">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -6920,48 +6920,48 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1.24161826</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>1.24199489</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>1.24212012</v>
+        <v>1.24161826</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>1.24224503</v>
+        <v>1.24199489</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>1.2423696</v>
+        <v>1.24212012</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>1.24249383</v>
+        <v>1.24224503</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>1.24286658</v>
+        <v>1.2423696</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>1.24299087</v>
+        <v>1.24249383</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>1.24311517</v>
+        <v>1.24286658</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1.24323913</v>
+        <v>1.24299087</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>1.24336207</v>
+        <v>1.24311517</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1.2437299</v>
+        <v>1.24323913</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>1.24385186</v>
+        <v>1.24336207</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>1.24397313</v>
+        <v>1.2437299</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>1.24409407</v>
+        <v>1.24385186</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>1.24421537</v>
+        <v>1.24397313</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>1.24470615</v>
+        <v>1.24409407</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>1.24483166</v>
+        <v>1.24421537</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>1.24495718</v>
+        <v>1.24470615</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>1.24508236</v>
+        <v>1.24483166</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>1.245459</v>
+        <v>1.24495718</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>1.24558528</v>
+        <v>1.24508236</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>1.24571087</v>
+        <v>1.245459</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>1.24583579</v>
+        <v>1.24558528</v>
       </c>
     </row>
     <row r="307">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>1.24596107</v>
+        <v>1.24571087</v>
       </c>
     </row>
     <row r="308">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>1.24633797</v>
+        <v>1.24583579</v>
       </c>
     </row>
     <row r="309">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>1.24646364</v>
+        <v>1.24596107</v>
       </c>
     </row>
     <row r="310">
@@ -7555,11 +7555,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>1.24658829</v>
+        <v>1.24633797</v>
       </c>
     </row>
     <row r="311">
@@ -7578,11 +7578,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>1.2467126</v>
+        <v>1.24646364</v>
       </c>
     </row>
     <row r="312">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>1.24683727</v>
+        <v>1.24658829</v>
       </c>
     </row>
     <row r="313">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>1.24721652</v>
+        <v>1.2467126</v>
       </c>
     </row>
     <row r="314">
@@ -7647,80 +7647,80 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>1.24734436</v>
+        <v>1.24683727</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>4.97</v>
+        <v>1.24721652</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>5.02</v>
+        <v>1.24734436</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>4.98</v>
+        <v>1.24747013</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="319">
@@ -7762,11 +7762,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="320">
@@ -7785,11 +7785,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="321">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="322">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>5.03</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="323">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="324">
@@ -7877,11 +7877,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>5.02</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="325">
@@ -7900,11 +7900,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>5.12</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="326">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>5.14</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="327">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="328">
@@ -7969,11 +7969,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="329">
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="330">
@@ -8015,11 +8015,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="331">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>5.03</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="332">
@@ -8061,11 +8061,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="333">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>4.98</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="334">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>4.99</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="335">
@@ -8130,11 +8130,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>4.99</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="336">
@@ -8153,11 +8153,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="337">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -8199,11 +8199,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="339">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>5.01</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="340">
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="341">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>5.01</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="342">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="343">
@@ -8314,11 +8314,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>4.95</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="344">
@@ -8337,11 +8337,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>4.97</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="345">
@@ -8360,80 +8360,80 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>4.97</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>1.91</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>1.95</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>1.96</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="349">
@@ -8452,11 +8452,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="350">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="351">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="352">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="353">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="354">
@@ -8567,11 +8567,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="355">
@@ -8590,11 +8590,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="356">
@@ -8613,11 +8613,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="357">
@@ -8636,11 +8636,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="358">
@@ -8659,11 +8659,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -8682,11 +8682,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="360">
@@ -8705,11 +8705,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="361">
@@ -8728,11 +8728,11 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="362">
@@ -8751,11 +8751,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="363">
@@ -8774,11 +8774,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="364">
@@ -8797,11 +8797,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="365">
@@ -8820,11 +8820,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="366">
@@ -8843,11 +8843,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="367">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="368">
@@ -8889,11 +8889,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="369">
@@ -8912,11 +8912,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="370">
@@ -8935,11 +8935,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="371">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="372">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="373">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="374">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="375">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="376">
@@ -9073,80 +9073,80 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="380">
@@ -9165,11 +9165,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="381">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="382">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="383">
@@ -9234,11 +9234,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="384">
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="385">
@@ -9280,11 +9280,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="386">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E386" t="n">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="388">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="389">
@@ -9372,11 +9372,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="390">
@@ -9395,11 +9395,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="391">
@@ -9418,11 +9418,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>2.39</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="392">
@@ -9441,11 +9441,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="393">
@@ -9464,11 +9464,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="394">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E394" t="n">
@@ -9510,11 +9510,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="396">
@@ -9533,11 +9533,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="397">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="398">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E399" t="n">
@@ -9625,11 +9625,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="401">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="402">
@@ -9671,11 +9671,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="403">
@@ -9694,11 +9694,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="404">
@@ -9717,11 +9717,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="405">
@@ -9740,11 +9740,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="406">
@@ -9763,11 +9763,11 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="407">
@@ -9786,11 +9786,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="408">
@@ -9809,10 +9809,79 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>15</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>15</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>15</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
           <t>20260616</t>
         </is>
       </c>
-      <c r="E408" t="n">
+      <c r="E411" t="n">
         <v>2.29</v>
       </c>
     </row>

--- a/data/mk_fred_data_master.xlsx
+++ b/data/mk_fred_data_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E525"/>
+  <dimension ref="A1:E538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,25 +1377,25 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>US2Y</t>
+          <t>US1Y</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>미국 국채 2년물 (CMT)</t>
+          <t>미국 국채 1년물 (CMT)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3.88</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="43">
@@ -1414,11 +1414,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="44">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="45">
@@ -1460,11 +1460,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="46">
@@ -1483,11 +1483,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="47">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="48">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="49">
@@ -1552,11 +1552,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="50">
@@ -1575,11 +1575,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="52">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -1644,11 +1644,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="54">
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="55">
@@ -1690,11 +1690,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="56">
@@ -1713,11 +1713,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="57">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="58">
@@ -1759,11 +1759,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4.01</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="59">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="60">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -1828,11 +1828,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="62">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="63">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1897,11 +1897,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="65">
@@ -1920,11 +1920,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="66">
@@ -1943,11 +1943,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="67">
@@ -1966,11 +1966,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="68">
@@ -1989,11 +1989,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="69">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2035,11 +2035,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="71">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="72">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="73">
@@ -2104,11 +2104,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="74">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="75">
@@ -2150,11 +2150,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="76">
@@ -2173,11 +2173,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="77">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="78">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="79">
@@ -2242,11 +2242,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="80">
@@ -2265,11 +2265,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="81">
@@ -2288,57 +2288,57 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>US3Y</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>미국 국채 3년물 (CMT)</t>
+          <t>미국 국채 2년물 (CMT)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>US3Y</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>미국 국채 3년물 (CMT)</t>
+          <t>미국 국채 2년물 (CMT)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3.98</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="84">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="85">
@@ -2380,11 +2380,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="86">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="87">
@@ -2426,11 +2426,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="88">
@@ -2449,11 +2449,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="89">
@@ -2472,11 +2472,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.01</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="90">
@@ -2495,11 +2495,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="91">
@@ -2518,11 +2518,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="92">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
@@ -2564,11 +2564,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="94">
@@ -2587,11 +2587,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="95">
@@ -2610,11 +2610,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="96">
@@ -2633,11 +2633,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="97">
@@ -2656,11 +2656,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="98">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="99">
@@ -2702,11 +2702,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4.09</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="100">
@@ -2725,11 +2725,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="101">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="102">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="103">
@@ -2794,11 +2794,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="104">
@@ -2817,11 +2817,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="105">
@@ -2840,11 +2840,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="106">
@@ -2863,11 +2863,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="107">
@@ -2886,11 +2886,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="108">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="109">
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="110">
@@ -2955,11 +2955,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="111">
@@ -2978,11 +2978,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="112">
@@ -3001,11 +3001,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="113">
@@ -3024,11 +3024,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="114">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="115">
@@ -3070,11 +3070,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4.19</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="116">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="117">
@@ -3116,11 +3116,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="118">
@@ -3139,11 +3139,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="119">
@@ -3162,11 +3162,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="120">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4.09</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="121">
@@ -3208,80 +3208,80 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4.02</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="125">
@@ -3300,11 +3300,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="126">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="127">
@@ -3346,11 +3346,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4.02</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="128">
@@ -3369,11 +3369,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4.07</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="129">
@@ -3392,11 +3392,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="130">
@@ -3415,11 +3415,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="131">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="132">
@@ -3461,11 +3461,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="133">
@@ -3484,11 +3484,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="134">
@@ -3507,11 +3507,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4.32</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="135">
@@ -3530,11 +3530,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="136">
@@ -3553,11 +3553,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="137">
@@ -3576,11 +3576,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="138">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="139">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="140">
@@ -3645,11 +3645,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="141">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="142">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="143">
@@ -3714,11 +3714,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="144">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="145">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -3783,11 +3783,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="147">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="148">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4.26</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="149">
@@ -3852,11 +3852,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="150">
@@ -3875,11 +3875,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="151">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="152">
@@ -3921,11 +3921,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4.18</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="153">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="154">
@@ -3967,11 +3967,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="155">
@@ -3990,11 +3990,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="156">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4.29</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="157">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="159">
@@ -4082,11 +4082,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="160">
@@ -4105,11 +4105,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4.12</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="161">
@@ -4128,103 +4128,103 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="166">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="167">
@@ -4266,11 +4266,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="168">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="169">
@@ -4312,11 +4312,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="170">
@@ -4335,11 +4335,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="171">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="172">
@@ -4381,11 +4381,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4.43</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="173">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="174">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="175">
@@ -4450,11 +4450,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="176">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="177">
@@ -4496,11 +4496,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="178">
@@ -4519,11 +4519,11 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="179">
@@ -4542,11 +4542,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="180">
@@ -4565,11 +4565,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4.27</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="182">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="183">
@@ -4634,11 +4634,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="184">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="185">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="186">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="187">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="188">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="189">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="190">
@@ -4795,11 +4795,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="191">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="192">
@@ -4841,11 +4841,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="193">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="194">
@@ -4887,11 +4887,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="195">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="197">
@@ -4956,11 +4956,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="198">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="199">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4.26</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="200">
@@ -5025,11 +5025,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4.23</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="201">
@@ -5048,126 +5048,126 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4.24</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4.39</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4.45</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4.43</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4.36</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4.41</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="207">
@@ -5186,11 +5186,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="208">
@@ -5209,11 +5209,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="209">
@@ -5232,11 +5232,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="210">
@@ -5255,11 +5255,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="211">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="212">
@@ -5301,11 +5301,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4.59</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="213">
@@ -5324,11 +5324,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="214">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="215">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="216">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="217">
@@ -5416,11 +5416,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="218">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="219">
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4.48</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="222">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="223">
@@ -5554,11 +5554,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="224">
@@ -5577,11 +5577,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="225">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="226">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="227">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="228">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4.53</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4.49</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="236">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="237">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="238">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="239">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="241">
@@ -5968,149 +5968,149 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4.38</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>3.59</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>3.61</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>3.61</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3.61</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>3.6</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="249">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6175,7 +6175,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="253">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E253" t="n">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="256">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="258">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="270">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="274">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="275">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="276">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="277">
@@ -6796,11 +6796,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="278">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="281">
@@ -6888,172 +6888,172 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>3.74</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>3.648</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3.647</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3.646</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3.645</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>3.643</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3.643</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>3.644</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3.643</v>
+        <v>3.648</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3.643</v>
+        <v>3.647</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3.642</v>
+        <v>3.646</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3.638</v>
+        <v>3.645</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>3.625</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>3.621</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>3.616</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3.612</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3.608</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3.594</v>
+        <v>3.642</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>3.593</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3.592</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3.592</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3.59</v>
+        <v>3.616</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3.591</v>
+        <v>3.612</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3.59</v>
+        <v>3.608</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3.59</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3.59</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="307">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3.593</v>
+        <v>3.592</v>
       </c>
     </row>
     <row r="309">
@@ -7532,11 +7532,11 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="310">
@@ -7555,11 +7555,11 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3.593</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="311">
@@ -7578,11 +7578,11 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="312">
@@ -7601,11 +7601,11 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>3.601</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="313">
@@ -7624,11 +7624,11 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>3.606</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="314">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>3.609</v>
+        <v>3.592</v>
       </c>
     </row>
     <row r="315">
@@ -7670,11 +7670,11 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3.612</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="316">
@@ -7693,11 +7693,11 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>3.626</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="317">
@@ -7716,11 +7716,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3.628</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>3.63</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="319">
@@ -7762,11 +7762,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>3.632</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="320">
@@ -7785,11 +7785,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>3.633</v>
+        <v>3.606</v>
       </c>
     </row>
     <row r="321">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>3.632</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="322">
@@ -7831,195 +7831,195 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>3.632</v>
+        <v>3.612</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>3.668</v>
+        <v>3.626</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>3.667</v>
+        <v>3.628</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>3.666</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>3.666</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>3.666</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>3.665</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>3.664</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>3.663</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="331">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>3.663</v>
+        <v>3.668</v>
       </c>
     </row>
     <row r="332">
@@ -8061,11 +8061,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3.662</v>
+        <v>3.667</v>
       </c>
     </row>
     <row r="333">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>3.661</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="334">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>3.657</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="335">
@@ -8130,11 +8130,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>3.655</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="336">
@@ -8153,11 +8153,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>3.653</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="337">
@@ -8176,11 +8176,11 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>3.651</v>
+        <v>3.664</v>
       </c>
     </row>
     <row r="338">
@@ -8199,11 +8199,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>3.649</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="339">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>3.644</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="340">
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>3.644</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="341">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3.643</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="342">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>3.643</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="343">
@@ -8314,11 +8314,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3.641</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="344">
@@ -8337,11 +8337,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>3.64</v>
+        <v>3.653</v>
       </c>
     </row>
     <row r="345">
@@ -8360,11 +8360,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>3.64</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="346">
@@ -8383,11 +8383,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>3.639</v>
+        <v>3.649</v>
       </c>
     </row>
     <row r="347">
@@ -8406,11 +8406,11 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>3.639</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="348">
@@ -8429,11 +8429,11 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>3.638</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="349">
@@ -8452,11 +8452,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>3.638</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="350">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>3.637</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="351">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>3.637</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="352">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>3.636</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="353">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>3.636</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="354">
@@ -8567,11 +8567,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>3.636</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="355">
@@ -8590,11 +8590,11 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>3.636</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="356">
@@ -8613,11 +8613,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>3.636</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="357">
@@ -8636,11 +8636,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>3.636</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="358">
@@ -8659,11 +8659,11 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="359">
@@ -8682,11 +8682,11 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="360">
@@ -8705,11 +8705,11 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="361">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E361" t="n">
@@ -8751,11 +8751,11 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="363">
@@ -8774,218 +8774,218 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>1.24161826</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>1.24199489</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>1.24212012</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>1.24224503</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>1.2423696</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>1.24249383</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>1.24286658</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>1.24299087</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>1.24311517</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="373">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>1.24323913</v>
+        <v>1.24161826</v>
       </c>
     </row>
     <row r="374">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>1.24336207</v>
+        <v>1.24199489</v>
       </c>
     </row>
     <row r="375">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>1.2437299</v>
+        <v>1.24212012</v>
       </c>
     </row>
     <row r="376">
@@ -9073,11 +9073,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>1.24385186</v>
+        <v>1.24224503</v>
       </c>
     </row>
     <row r="377">
@@ -9096,11 +9096,11 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>1.24397313</v>
+        <v>1.2423696</v>
       </c>
     </row>
     <row r="378">
@@ -9119,11 +9119,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>1.24409407</v>
+        <v>1.24249383</v>
       </c>
     </row>
     <row r="379">
@@ -9142,11 +9142,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>1.24421537</v>
+        <v>1.24286658</v>
       </c>
     </row>
     <row r="380">
@@ -9165,11 +9165,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>1.24470615</v>
+        <v>1.24299087</v>
       </c>
     </row>
     <row r="381">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>1.24483166</v>
+        <v>1.24311517</v>
       </c>
     </row>
     <row r="382">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>1.24495718</v>
+        <v>1.24323913</v>
       </c>
     </row>
     <row r="383">
@@ -9234,11 +9234,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>1.24508236</v>
+        <v>1.24336207</v>
       </c>
     </row>
     <row r="384">
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>1.245459</v>
+        <v>1.2437299</v>
       </c>
     </row>
     <row r="385">
@@ -9280,11 +9280,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>1.24558528</v>
+        <v>1.24385186</v>
       </c>
     </row>
     <row r="386">
@@ -9303,11 +9303,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>1.24571087</v>
+        <v>1.24397313</v>
       </c>
     </row>
     <row r="387">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>1.24583579</v>
+        <v>1.24409407</v>
       </c>
     </row>
     <row r="388">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>1.24596107</v>
+        <v>1.24421537</v>
       </c>
     </row>
     <row r="389">
@@ -9372,11 +9372,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>1.24633797</v>
+        <v>1.24470615</v>
       </c>
     </row>
     <row r="390">
@@ -9395,11 +9395,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>1.24646364</v>
+        <v>1.24483166</v>
       </c>
     </row>
     <row r="391">
@@ -9418,11 +9418,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>1.24658829</v>
+        <v>1.24495718</v>
       </c>
     </row>
     <row r="392">
@@ -9441,11 +9441,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>1.2467126</v>
+        <v>1.24508236</v>
       </c>
     </row>
     <row r="393">
@@ -9464,11 +9464,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>1.24683727</v>
+        <v>1.245459</v>
       </c>
     </row>
     <row r="394">
@@ -9487,11 +9487,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>1.24721652</v>
+        <v>1.24558528</v>
       </c>
     </row>
     <row r="395">
@@ -9510,11 +9510,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>1.24734436</v>
+        <v>1.24571087</v>
       </c>
     </row>
     <row r="396">
@@ -9533,11 +9533,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>1.24747013</v>
+        <v>1.24583579</v>
       </c>
     </row>
     <row r="397">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>1.24759592</v>
+        <v>1.24596107</v>
       </c>
     </row>
     <row r="398">
@@ -9579,11 +9579,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>1.24809773</v>
+        <v>1.24633797</v>
       </c>
     </row>
     <row r="399">
@@ -9602,11 +9602,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>1.24822289</v>
+        <v>1.24646364</v>
       </c>
     </row>
     <row r="400">
@@ -9625,11 +9625,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>1.2483484</v>
+        <v>1.24658829</v>
       </c>
     </row>
     <row r="401">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>1.24847393</v>
+        <v>1.2467126</v>
       </c>
     </row>
     <row r="402">
@@ -9671,11 +9671,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1.24860016</v>
+        <v>1.24683727</v>
       </c>
     </row>
     <row r="403">
@@ -9694,11 +9694,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1.24897683</v>
+        <v>1.24721652</v>
       </c>
     </row>
     <row r="404">
@@ -9717,241 +9717,241 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1.24910242</v>
+        <v>1.24734436</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>4.97</v>
+        <v>1.24747013</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>5.02</v>
+        <v>1.24759592</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>4.98</v>
+        <v>1.24809773</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>4.94</v>
+        <v>1.24822289</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>4.97</v>
+        <v>1.2483484</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>4.95</v>
+        <v>1.24847393</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>4.98</v>
+        <v>1.24860016</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>5.03</v>
+        <v>1.24897683</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>5.03</v>
+        <v>1.24910242</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>5.02</v>
+        <v>1.2492301</v>
       </c>
     </row>
     <row r="415">
@@ -9970,11 +9970,11 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>5.12</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="416">
@@ -9993,11 +9993,11 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>5.14</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="417">
@@ -10016,11 +10016,11 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="418">
@@ -10039,11 +10039,11 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>5.11</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="419">
@@ -10062,11 +10062,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="420">
@@ -10085,11 +10085,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="421">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="422">
@@ -10131,11 +10131,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="423">
@@ -10154,11 +10154,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="424">
@@ -10177,11 +10177,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="425">
@@ -10200,11 +10200,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>4.99</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="426">
@@ -10223,11 +10223,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>4.97</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="427">
@@ -10246,11 +10246,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>4.99</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="428">
@@ -10269,11 +10269,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>4.97</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="429">
@@ -10292,11 +10292,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="430">
@@ -10315,11 +10315,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="431">
@@ -10338,11 +10338,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="432">
@@ -10361,11 +10361,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="433">
@@ -10384,11 +10384,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="434">
@@ -10407,11 +10407,11 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="435">
@@ -10430,11 +10430,11 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="436">
@@ -10453,11 +10453,11 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="437">
@@ -10476,11 +10476,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>4.93</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="438">
@@ -10499,11 +10499,11 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="439">
@@ -10522,11 +10522,11 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="440">
@@ -10545,11 +10545,11 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>4.94</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="441">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>4.86</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="442">
@@ -10591,11 +10591,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>4.86</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="443">
@@ -10614,11 +10614,11 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="444">
@@ -10637,264 +10637,264 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>4.86</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>1.91</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>1.95</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>1.96</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>1.94</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>1.96</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>1.93</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>1.95</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>1.99</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>1.99</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>2</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>2.1</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="456">
@@ -10913,11 +10913,11 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="457">
@@ -10936,11 +10936,11 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="458">
@@ -10959,11 +10959,11 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="459">
@@ -10982,11 +10982,11 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="460">
@@ -11005,11 +11005,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="461">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="462">
@@ -11051,11 +11051,11 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="463">
@@ -11074,11 +11074,11 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="464">
@@ -11097,11 +11097,11 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="465">
@@ -11120,11 +11120,11 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="466">
@@ -11143,11 +11143,11 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="467">
@@ -11166,11 +11166,11 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="468">
@@ -11189,11 +11189,11 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="469">
@@ -11212,11 +11212,11 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E469" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="470">
@@ -11235,11 +11235,11 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="471">
@@ -11258,11 +11258,11 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="472">
@@ -11281,11 +11281,11 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="473">
@@ -11304,11 +11304,11 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="474">
@@ -11327,11 +11327,11 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="475">
@@ -11350,11 +11350,11 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="476">
@@ -11373,11 +11373,11 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="477">
@@ -11396,11 +11396,11 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="478">
@@ -11419,11 +11419,11 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="479">
@@ -11442,11 +11442,11 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="480">
@@ -11465,11 +11465,11 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="481">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="482">
@@ -11511,11 +11511,11 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="483">
@@ -11534,11 +11534,11 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="484">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -11566,278 +11566,278 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>2.47</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>2.45</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>2.47</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="497">
@@ -11856,11 +11856,11 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="498">
@@ -11879,11 +11879,11 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="499">
@@ -11902,11 +11902,11 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="500">
@@ -11925,11 +11925,11 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="501">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="502">
@@ -11971,11 +11971,11 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="503">
@@ -11994,11 +11994,11 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="504">
@@ -12017,11 +12017,11 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="505">
@@ -12040,11 +12040,11 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="506">
@@ -12063,11 +12063,11 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="507">
@@ -12086,11 +12086,11 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="508">
@@ -12109,11 +12109,11 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="509">
@@ -12132,11 +12132,11 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="510">
@@ -12155,11 +12155,11 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="511">
@@ -12178,11 +12178,11 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="512">
@@ -12201,11 +12201,11 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="513">
@@ -12224,11 +12224,11 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="514">
@@ -12247,11 +12247,11 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="515">
@@ -12270,11 +12270,11 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="516">
@@ -12293,11 +12293,11 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="517">
@@ -12316,11 +12316,11 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="518">
@@ -12339,11 +12339,11 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="519">
@@ -12362,11 +12362,11 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="520">
@@ -12385,11 +12385,11 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E520" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="521">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="522">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="523">
@@ -12454,11 +12454,11 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="524">
@@ -12477,11 +12477,11 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="525">
@@ -12500,11 +12500,310 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
+          <t>20260611</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>15</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>20260612</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>15</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>20260615</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>15</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>20260616</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>15</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>20260617</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>15</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>20260618</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>15</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>20260622</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>15</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>20260623</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>15</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>20260624</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>15</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>20260625</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>15</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>20260626</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>15</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>15</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
           <t>20260630</t>
         </is>
       </c>
-      <c r="E525" t="n">
+      <c r="E537" t="n">
         <v>2.24</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>15</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>2.23</v>
       </c>
     </row>
   </sheetData>

--- a/data/mk_fred_data_master.xlsx
+++ b/data/mk_fred_data_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E577"/>
+  <dimension ref="A1:E590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,25 +1469,25 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>US2Y</t>
+          <t>US1Y</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>미국 국채 2년물 (CMT)</t>
+          <t>미국 국채 1년물 (CMT)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="47">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="48">
@@ -1529,11 +1529,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="49">
@@ -1552,11 +1552,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="50">
@@ -1575,11 +1575,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="51">
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="52">
@@ -1621,11 +1621,11 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="53">
@@ -1644,11 +1644,11 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="54">
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -1690,11 +1690,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="56">
@@ -1713,11 +1713,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="58">
@@ -1759,11 +1759,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="59">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="60">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="61">
@@ -1828,11 +1828,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="62">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4.01</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="63">
@@ -1874,11 +1874,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="64">
@@ -1897,11 +1897,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -1920,11 +1920,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="66">
@@ -1943,11 +1943,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="67">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -1989,11 +1989,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="69">
@@ -2012,11 +2012,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="70">
@@ -2035,11 +2035,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="71">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="72">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="73">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="75">
@@ -2150,11 +2150,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="76">
@@ -2173,11 +2173,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="77">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="78">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="79">
@@ -2242,11 +2242,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="80">
@@ -2265,11 +2265,11 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="81">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="82">
@@ -2311,11 +2311,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="83">
@@ -2334,11 +2334,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="84">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="85">
@@ -2380,11 +2380,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="86">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="87">
@@ -2426,11 +2426,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="88">
@@ -2449,11 +2449,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="89">
@@ -2472,57 +2472,57 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>US3Y</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>미국 국채 3년물 (CMT)</t>
+          <t>미국 국채 2년물 (CMT)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3.91</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>US3Y</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>미국 국채 3년물 (CMT)</t>
+          <t>미국 국채 2년물 (CMT)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3.98</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="92">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="93">
@@ -2564,11 +2564,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="94">
@@ -2587,11 +2587,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="95">
@@ -2610,11 +2610,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="96">
@@ -2633,11 +2633,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="97">
@@ -2656,11 +2656,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.01</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="98">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="99">
@@ -2702,11 +2702,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="100">
@@ -2725,11 +2725,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="102">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="103">
@@ -2794,11 +2794,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="104">
@@ -2817,11 +2817,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="105">
@@ -2840,11 +2840,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="106">
@@ -2863,11 +2863,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="107">
@@ -2886,11 +2886,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4.09</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="108">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="109">
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="110">
@@ -2955,11 +2955,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="111">
@@ -2978,11 +2978,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="112">
@@ -3001,11 +3001,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="113">
@@ -3024,11 +3024,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="114">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="115">
@@ -3070,11 +3070,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="116">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="117">
@@ -3116,11 +3116,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="118">
@@ -3139,11 +3139,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="119">
@@ -3162,11 +3162,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="120">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="121">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="122">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="123">
@@ -3254,11 +3254,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4.19</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="124">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="125">
@@ -3300,11 +3300,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="126">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="127">
@@ -3346,11 +3346,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="128">
@@ -3369,11 +3369,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4.09</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="129">
@@ -3392,11 +3392,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="130">
@@ -3415,11 +3415,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4.15</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="131">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="132">
@@ -3461,11 +3461,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="133">
@@ -3484,80 +3484,80 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4.02</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4.08</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="137">
@@ -3576,11 +3576,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="138">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="139">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4.02</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="140">
@@ -3645,11 +3645,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4.07</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="141">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="142">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="143">
@@ -3714,11 +3714,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="144">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="145">
@@ -3760,11 +3760,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="146">
@@ -3783,11 +3783,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4.32</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="147">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="148">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="149">
@@ -3852,11 +3852,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="150">
@@ -3875,11 +3875,11 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="151">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="152">
@@ -3921,11 +3921,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="153">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="154">
@@ -3967,11 +3967,11 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="155">
@@ -3990,11 +3990,11 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="156">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="157">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="159">
@@ -4082,11 +4082,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="160">
@@ -4105,11 +4105,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4.26</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="161">
@@ -4128,11 +4128,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="162">
@@ -4151,11 +4151,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="163">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="164">
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4.18</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="165">
@@ -4220,11 +4220,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="166">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="167">
@@ -4266,11 +4266,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="168">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4.29</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="169">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4335,11 +4335,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="171">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="172">
@@ -4381,11 +4381,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4.12</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="173">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="174">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="175">
@@ -4450,11 +4450,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4.24</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="176">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="177">
@@ -4496,103 +4496,103 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4.26</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4.17</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="182">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="183">
@@ -4634,11 +4634,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="184">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="185">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="186">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="187">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="188">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4.43</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="189">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="190">
@@ -4795,11 +4795,11 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="191">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="192">
@@ -4841,11 +4841,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="193">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="194">
@@ -4887,11 +4887,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="195">
@@ -4910,11 +4910,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="196">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="197">
@@ -4956,11 +4956,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4.27</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="198">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="199">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="200">
@@ -5025,11 +5025,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="201">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="202">
@@ -5071,11 +5071,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="203">
@@ -5094,11 +5094,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="204">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="205">
@@ -5140,11 +5140,11 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="206">
@@ -5163,11 +5163,11 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="207">
@@ -5186,11 +5186,11 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="208">
@@ -5209,11 +5209,11 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="209">
@@ -5232,11 +5232,11 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="210">
@@ -5255,11 +5255,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="211">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5301,11 +5301,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="213">
@@ -5324,11 +5324,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="214">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="215">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4.26</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="216">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4.23</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="217">
@@ -5416,11 +5416,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4.24</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="218">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="219">
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4.35</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4.35</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="221">
@@ -5508,126 +5508,126 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4.39</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4.45</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4.43</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="227">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="228">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4.59</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="236">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="237">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="238">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="239">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4.48</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="241">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="242">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="243">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="244">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="245">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="246">
@@ -6083,11 +6083,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="247">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>4.53</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4.49</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="256">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="259">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>4.38</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="265">
@@ -6520,149 +6520,149 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>3.59</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>3.61</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>3.61</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3.61</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>3.61</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>3.6</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="273">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E274" t="n">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="276">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="277">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E277" t="n">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="282">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E282" t="n">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="284">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="294">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>3.74</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="307">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="308">
@@ -7509,11 +7509,11 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="309">
@@ -7532,172 +7532,172 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3.648</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3.647</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>3.646</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>3.645</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>3.643</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>3.643</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>3.644</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="317">
@@ -7716,11 +7716,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3.643</v>
+        <v>3.648</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>3.643</v>
+        <v>3.647</v>
       </c>
     </row>
     <row r="319">
@@ -7762,11 +7762,11 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>3.642</v>
+        <v>3.646</v>
       </c>
     </row>
     <row r="320">
@@ -7785,11 +7785,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>3.638</v>
+        <v>3.645</v>
       </c>
     </row>
     <row r="321">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>3.625</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="322">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>3.621</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="323">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>3.616</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="324">
@@ -7877,11 +7877,11 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>3.612</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="325">
@@ -7900,11 +7900,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>3.608</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="326">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>3.594</v>
+        <v>3.642</v>
       </c>
     </row>
     <row r="327">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>3.593</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="328">
@@ -7969,11 +7969,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>3.592</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="329">
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>3.592</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="330">
@@ -8015,11 +8015,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>3.59</v>
+        <v>3.616</v>
       </c>
     </row>
     <row r="331">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>3.591</v>
+        <v>3.612</v>
       </c>
     </row>
     <row r="332">
@@ -8061,11 +8061,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3.59</v>
+        <v>3.608</v>
       </c>
     </row>
     <row r="333">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>3.59</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="334">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>3.59</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="335">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -8153,11 +8153,11 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>3.593</v>
+        <v>3.592</v>
       </c>
     </row>
     <row r="337">
@@ -8176,11 +8176,11 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="338">
@@ -8199,11 +8199,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>3.593</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="339">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="340">
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>3.601</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="341">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3.606</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="342">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>3.609</v>
+        <v>3.592</v>
       </c>
     </row>
     <row r="343">
@@ -8314,11 +8314,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3.612</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="344">
@@ -8337,11 +8337,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>3.626</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="345">
@@ -8360,11 +8360,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>3.628</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="346">
@@ -8383,11 +8383,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>3.63</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="347">
@@ -8406,11 +8406,11 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>3.632</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="348">
@@ -8429,11 +8429,11 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>3.633</v>
+        <v>3.606</v>
       </c>
     </row>
     <row r="349">
@@ -8452,11 +8452,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>3.632</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="350">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>3.632</v>
+        <v>3.612</v>
       </c>
     </row>
     <row r="351">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>3.633</v>
+        <v>3.626</v>
       </c>
     </row>
     <row r="352">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>3.634</v>
+        <v>3.628</v>
       </c>
     </row>
     <row r="353">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>3.636</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="354">
@@ -8567,195 +8567,195 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>3.636</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>3.668</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>3.667</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>3.666</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>3.666</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>3.666</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>3.665</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>3.664</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>3.663</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="363">
@@ -8774,11 +8774,11 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>3.663</v>
+        <v>3.668</v>
       </c>
     </row>
     <row r="364">
@@ -8797,11 +8797,11 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>3.662</v>
+        <v>3.667</v>
       </c>
     </row>
     <row r="365">
@@ -8820,11 +8820,11 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>3.661</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="366">
@@ -8843,11 +8843,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>3.657</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="367">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>3.655</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="368">
@@ -8889,11 +8889,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>3.653</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="369">
@@ -8912,11 +8912,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>3.651</v>
+        <v>3.664</v>
       </c>
     </row>
     <row r="370">
@@ -8935,11 +8935,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>3.649</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="371">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>3.644</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="372">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>3.644</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="373">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>3.643</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="374">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>3.643</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="375">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>3.641</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="376">
@@ -9073,11 +9073,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>3.64</v>
+        <v>3.653</v>
       </c>
     </row>
     <row r="377">
@@ -9096,11 +9096,11 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>3.64</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="378">
@@ -9119,11 +9119,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>3.639</v>
+        <v>3.649</v>
       </c>
     </row>
     <row r="379">
@@ -9142,11 +9142,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>3.639</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="380">
@@ -9165,11 +9165,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>3.638</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="381">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>3.638</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="382">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>3.637</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="383">
@@ -9234,11 +9234,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>3.637</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="384">
@@ -9257,11 +9257,11 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>3.636</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="385">
@@ -9280,11 +9280,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>3.636</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="386">
@@ -9303,11 +9303,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>3.636</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="387">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>3.636</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="388">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>3.636</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="389">
@@ -9372,11 +9372,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>3.636</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="390">
@@ -9395,11 +9395,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="391">
@@ -9418,11 +9418,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="392">
@@ -9441,11 +9441,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="393">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E393" t="n">
@@ -9487,11 +9487,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="395">
@@ -9510,11 +9510,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="396">
@@ -9533,11 +9533,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="397">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="398">
@@ -9579,11 +9579,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>3.634</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="399">
@@ -9602,218 +9602,218 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>3.634</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>1.24161826</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>1.24199489</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>1.24212012</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>1.24224503</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>1.2423696</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>1.24249383</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>1.24286658</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>1.24299087</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>1.24311517</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="409">
@@ -9832,11 +9832,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>1.24323913</v>
+        <v>1.24161826</v>
       </c>
     </row>
     <row r="410">
@@ -9855,11 +9855,11 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>1.24336207</v>
+        <v>1.24199489</v>
       </c>
     </row>
     <row r="411">
@@ -9878,11 +9878,11 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>1.2437299</v>
+        <v>1.24212012</v>
       </c>
     </row>
     <row r="412">
@@ -9901,11 +9901,11 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>1.24385186</v>
+        <v>1.24224503</v>
       </c>
     </row>
     <row r="413">
@@ -9924,11 +9924,11 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>1.24397313</v>
+        <v>1.2423696</v>
       </c>
     </row>
     <row r="414">
@@ -9947,11 +9947,11 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>1.24409407</v>
+        <v>1.24249383</v>
       </c>
     </row>
     <row r="415">
@@ -9970,11 +9970,11 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>1.24421537</v>
+        <v>1.24286658</v>
       </c>
     </row>
     <row r="416">
@@ -9993,11 +9993,11 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>1.24470615</v>
+        <v>1.24299087</v>
       </c>
     </row>
     <row r="417">
@@ -10016,11 +10016,11 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>1.24483166</v>
+        <v>1.24311517</v>
       </c>
     </row>
     <row r="418">
@@ -10039,11 +10039,11 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>1.24495718</v>
+        <v>1.24323913</v>
       </c>
     </row>
     <row r="419">
@@ -10062,11 +10062,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>1.24508236</v>
+        <v>1.24336207</v>
       </c>
     </row>
     <row r="420">
@@ -10085,11 +10085,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>1.245459</v>
+        <v>1.2437299</v>
       </c>
     </row>
     <row r="421">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>1.24558528</v>
+        <v>1.24385186</v>
       </c>
     </row>
     <row r="422">
@@ -10131,11 +10131,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>1.24571087</v>
+        <v>1.24397313</v>
       </c>
     </row>
     <row r="423">
@@ -10154,11 +10154,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>1.24583579</v>
+        <v>1.24409407</v>
       </c>
     </row>
     <row r="424">
@@ -10177,11 +10177,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>1.24596107</v>
+        <v>1.24421537</v>
       </c>
     </row>
     <row r="425">
@@ -10200,11 +10200,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>1.24633797</v>
+        <v>1.24470615</v>
       </c>
     </row>
     <row r="426">
@@ -10223,11 +10223,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>1.24646364</v>
+        <v>1.24483166</v>
       </c>
     </row>
     <row r="427">
@@ -10246,11 +10246,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>1.24658829</v>
+        <v>1.24495718</v>
       </c>
     </row>
     <row r="428">
@@ -10269,11 +10269,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>1.2467126</v>
+        <v>1.24508236</v>
       </c>
     </row>
     <row r="429">
@@ -10292,11 +10292,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>1.24683727</v>
+        <v>1.245459</v>
       </c>
     </row>
     <row r="430">
@@ -10315,11 +10315,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>1.24721652</v>
+        <v>1.24558528</v>
       </c>
     </row>
     <row r="431">
@@ -10338,11 +10338,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>1.24734436</v>
+        <v>1.24571087</v>
       </c>
     </row>
     <row r="432">
@@ -10361,11 +10361,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>1.24747013</v>
+        <v>1.24583579</v>
       </c>
     </row>
     <row r="433">
@@ -10384,11 +10384,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>1.24759592</v>
+        <v>1.24596107</v>
       </c>
     </row>
     <row r="434">
@@ -10407,11 +10407,11 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>1.24809773</v>
+        <v>1.24633797</v>
       </c>
     </row>
     <row r="435">
@@ -10430,11 +10430,11 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>1.24822289</v>
+        <v>1.24646364</v>
       </c>
     </row>
     <row r="436">
@@ -10453,11 +10453,11 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>1.2483484</v>
+        <v>1.24658829</v>
       </c>
     </row>
     <row r="437">
@@ -10476,11 +10476,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>1.24847393</v>
+        <v>1.2467126</v>
       </c>
     </row>
     <row r="438">
@@ -10499,11 +10499,11 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>1.24860016</v>
+        <v>1.24683727</v>
       </c>
     </row>
     <row r="439">
@@ -10522,11 +10522,11 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>1.24897683</v>
+        <v>1.24721652</v>
       </c>
     </row>
     <row r="440">
@@ -10545,11 +10545,11 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>1.24910242</v>
+        <v>1.24734436</v>
       </c>
     </row>
     <row r="441">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>1.2492301</v>
+        <v>1.24747013</v>
       </c>
     </row>
     <row r="442">
@@ -10591,11 +10591,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>1.24935711</v>
+        <v>1.24759592</v>
       </c>
     </row>
     <row r="443">
@@ -10614,11 +10614,11 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>1.2498624</v>
+        <v>1.24809773</v>
       </c>
     </row>
     <row r="444">
@@ -10637,241 +10637,241 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>1.24998843</v>
+        <v>1.24822289</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>4.97</v>
+        <v>1.2483484</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>5.02</v>
+        <v>1.24847393</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>4.98</v>
+        <v>1.24860016</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>4.94</v>
+        <v>1.24897683</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E449" t="n">
-        <v>4.97</v>
+        <v>1.24910242</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>4.95</v>
+        <v>1.2492301</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>4.98</v>
+        <v>1.24935711</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>5.03</v>
+        <v>1.2498624</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>5.03</v>
+        <v>1.24998843</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>5.02</v>
+        <v>1.25011412</v>
       </c>
     </row>
     <row r="455">
@@ -10890,11 +10890,11 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>5.12</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="456">
@@ -10913,11 +10913,11 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E456" t="n">
-        <v>5.14</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="457">
@@ -10936,11 +10936,11 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="458">
@@ -10959,11 +10959,11 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>5.11</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="459">
@@ -10982,11 +10982,11 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="460">
@@ -11005,11 +11005,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="461">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="462">
@@ -11051,11 +11051,11 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="463">
@@ -11074,11 +11074,11 @@
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="464">
@@ -11097,11 +11097,11 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="465">
@@ -11120,11 +11120,11 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>4.99</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="466">
@@ -11143,11 +11143,11 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>4.97</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="467">
@@ -11166,11 +11166,11 @@
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>4.99</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="468">
@@ -11189,11 +11189,11 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>4.97</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="469">
@@ -11212,11 +11212,11 @@
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E469" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="470">
@@ -11235,11 +11235,11 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="471">
@@ -11258,11 +11258,11 @@
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="472">
@@ -11281,11 +11281,11 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="473">
@@ -11304,11 +11304,11 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="474">
@@ -11327,11 +11327,11 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="475">
@@ -11350,11 +11350,11 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="476">
@@ -11373,11 +11373,11 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="477">
@@ -11396,11 +11396,11 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>4.93</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="478">
@@ -11419,11 +11419,11 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="479">
@@ -11442,11 +11442,11 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="480">
@@ -11465,11 +11465,11 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>4.94</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="481">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>4.86</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="482">
@@ -11511,11 +11511,11 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>4.86</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="483">
@@ -11534,11 +11534,11 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="484">
@@ -11557,11 +11557,11 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E484" t="n">
-        <v>4.86</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="485">
@@ -11580,11 +11580,11 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="486">
@@ -11603,11 +11603,11 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>4.97</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="487">
@@ -11626,11 +11626,11 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>4.98</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="488">
@@ -11649,264 +11649,264 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>1.91</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>1.95</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>1.96</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>1.94</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>1.96</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>1.93</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>1.95</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>1.99</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>1.99</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>2</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>2.1</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="500">
@@ -11925,11 +11925,11 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="501">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="502">
@@ -11971,11 +11971,11 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="503">
@@ -11994,11 +11994,11 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="504">
@@ -12017,11 +12017,11 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="505">
@@ -12040,11 +12040,11 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="506">
@@ -12063,11 +12063,11 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="507">
@@ -12086,11 +12086,11 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="508">
@@ -12109,11 +12109,11 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="509">
@@ -12132,11 +12132,11 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510">
@@ -12155,11 +12155,11 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="511">
@@ -12178,11 +12178,11 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="512">
@@ -12201,11 +12201,11 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="513">
@@ -12224,11 +12224,11 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="514">
@@ -12247,11 +12247,11 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="515">
@@ -12270,11 +12270,11 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="516">
@@ -12293,11 +12293,11 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="517">
@@ -12316,11 +12316,11 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="518">
@@ -12339,11 +12339,11 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="519">
@@ -12362,11 +12362,11 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="520">
@@ -12385,11 +12385,11 @@
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E520" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="521">
@@ -12408,11 +12408,11 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="522">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="523">
@@ -12454,11 +12454,11 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="524">
@@ -12477,11 +12477,11 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="525">
@@ -12500,11 +12500,11 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="526">
@@ -12523,11 +12523,11 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="527">
@@ -12546,11 +12546,11 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="528">
@@ -12569,7 +12569,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E528" t="n">
@@ -12592,11 +12592,11 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E529" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="530">
@@ -12615,11 +12615,11 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="531">
@@ -12638,11 +12638,11 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="532">
@@ -12661,287 +12661,287 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E534" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E535" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E536" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E537" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="545">
@@ -12960,11 +12960,11 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="546">
@@ -12983,11 +12983,11 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="547">
@@ -13006,11 +13006,11 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="548">
@@ -13029,11 +13029,11 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="549">
@@ -13052,11 +13052,11 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="550">
@@ -13075,11 +13075,11 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="551">
@@ -13098,11 +13098,11 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="552">
@@ -13121,11 +13121,11 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E552" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="553">
@@ -13144,11 +13144,11 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="554">
@@ -13167,11 +13167,11 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E554" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="555">
@@ -13190,11 +13190,11 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="556">
@@ -13213,11 +13213,11 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="557">
@@ -13236,11 +13236,11 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="558">
@@ -13259,11 +13259,11 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="559">
@@ -13282,11 +13282,11 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="560">
@@ -13305,11 +13305,11 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="561">
@@ -13328,11 +13328,11 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="562">
@@ -13351,11 +13351,11 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="563">
@@ -13374,11 +13374,11 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="564">
@@ -13397,11 +13397,11 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E564" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="565">
@@ -13420,11 +13420,11 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E565" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="566">
@@ -13443,11 +13443,11 @@
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E566" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="567">
@@ -13466,11 +13466,11 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="568">
@@ -13489,11 +13489,11 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E568" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="569">
@@ -13512,11 +13512,11 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E569" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="570">
@@ -13535,11 +13535,11 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E570" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="571">
@@ -13558,11 +13558,11 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E571" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="572">
@@ -13581,11 +13581,11 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="573">
@@ -13604,11 +13604,11 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="574">
@@ -13627,11 +13627,11 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="575">
@@ -13650,11 +13650,11 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E575" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="576">
@@ -13673,11 +13673,11 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E576" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="577">
@@ -13696,10 +13696,309 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
+          <t>20260617</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>15</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>20260618</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>15</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>20260622</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>15</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>20260623</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>15</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>20260624</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>15</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>20260625</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>15</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>20260626</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>15</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>20260629</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>15</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>15</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>15</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>15</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>20260706</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>15</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
           <t>20260707</t>
         </is>
       </c>
-      <c r="E577" t="n">
+      <c r="E589" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>15</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
         <v>2.25</v>
       </c>
     </row>

--- a/data/mk_fred_data_master.xlsx
+++ b/data/mk_fred_data_master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E668"/>
+  <dimension ref="A1:E681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,25 +1630,25 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US2Y</t>
+          <t>US1Y</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>미국 국채 2년물 (CMT)</t>
+          <t>미국 국채 1년물 (CMT)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3.88</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="54">
@@ -1667,11 +1667,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3.95</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="55">
@@ -1690,11 +1690,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="56">
@@ -1713,11 +1713,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="57">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="58">
@@ -1759,11 +1759,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="59">
@@ -1782,11 +1782,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="60">
@@ -1805,11 +1805,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="61">
@@ -1828,11 +1828,11 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="63">
@@ -1874,11 +1874,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -1897,11 +1897,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="65">
@@ -1920,11 +1920,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="66">
@@ -1943,11 +1943,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4.04</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="67">
@@ -1966,11 +1966,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="68">
@@ -1989,11 +1989,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="69">
@@ -2012,11 +2012,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4.01</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="70">
@@ -2035,11 +2035,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="71">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="73">
@@ -2104,11 +2104,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="74">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2150,11 +2150,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="76">
@@ -2173,11 +2173,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="77">
@@ -2196,11 +2196,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4.17</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="78">
@@ -2219,11 +2219,11 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="79">
@@ -2242,11 +2242,11 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="80">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4.05</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="82">
@@ -2311,11 +2311,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="83">
@@ -2334,11 +2334,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="84">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="85">
@@ -2380,11 +2380,11 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="86">
@@ -2403,11 +2403,11 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="87">
@@ -2426,11 +2426,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="88">
@@ -2449,11 +2449,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4.16</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="89">
@@ -2472,11 +2472,11 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="90">
@@ -2495,11 +2495,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="91">
@@ -2518,11 +2518,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="92">
@@ -2541,11 +2541,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="93">
@@ -2564,11 +2564,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="94">
@@ -2587,11 +2587,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="95">
@@ -2610,11 +2610,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="96">
@@ -2633,11 +2633,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4.13</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="97">
@@ -2656,11 +2656,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.19</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="98">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="99">
@@ -2702,11 +2702,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4.16</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="100">
@@ -2725,11 +2725,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="101">
@@ -2748,11 +2748,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="102">
@@ -2771,11 +2771,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4.18</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="103">
@@ -2794,57 +2794,57 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>US3Y</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>미국 국채 3년물 (CMT)</t>
+          <t>미국 국채 2년물 (CMT)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>3.91</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>US3Y</t>
+          <t>US2Y</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>미국 국채 3년물 (CMT)</t>
+          <t>미국 국채 2년물 (CMT)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>3.98</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="106">
@@ -2863,11 +2863,11 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="107">
@@ -2886,11 +2886,11 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3.89</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="108">
@@ -2909,11 +2909,11 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="109">
@@ -2932,11 +2932,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="110">
@@ -2955,11 +2955,11 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="111">
@@ -2978,11 +2978,11 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4.01</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="112">
@@ -3001,11 +3001,11 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="113">
@@ -3024,11 +3024,11 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="114">
@@ -3047,11 +3047,11 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -3070,11 +3070,11 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4.14</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="116">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="117">
@@ -3116,11 +3116,11 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="118">
@@ -3139,11 +3139,11 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="119">
@@ -3162,11 +3162,11 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="120">
@@ -3185,11 +3185,11 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="121">
@@ -3208,11 +3208,11 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4.09</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="122">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="123">
@@ -3254,11 +3254,11 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4.06</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="124">
@@ -3277,11 +3277,11 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="125">
@@ -3300,11 +3300,11 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="126">
@@ -3323,11 +3323,11 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="127">
@@ -3346,11 +3346,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="128">
@@ -3369,11 +3369,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4.22</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="129">
@@ -3392,11 +3392,11 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="130">
@@ -3415,11 +3415,11 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4.16</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="131">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="132">
@@ -3461,11 +3461,11 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4.09</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="133">
@@ -3484,11 +3484,11 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="134">
@@ -3507,11 +3507,11 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="135">
@@ -3530,11 +3530,11 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="136">
@@ -3553,11 +3553,11 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4.23</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="137">
@@ -3576,11 +3576,11 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4.19</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="138">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="139">
@@ -3622,11 +3622,11 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="140">
@@ -3645,11 +3645,11 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="141">
@@ -3668,11 +3668,11 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4.13</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="142">
@@ -3691,11 +3691,11 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4.09</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="143">
@@ -3714,11 +3714,11 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="144">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4.15</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="145">
@@ -3760,11 +3760,11 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="146">
@@ -3783,11 +3783,11 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="147">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4.14</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="148">
@@ -3829,11 +3829,11 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="149">
@@ -3852,11 +3852,11 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4.21</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="150">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -3898,11 +3898,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="152">
@@ -3921,11 +3921,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="153">
@@ -3944,11 +3944,11 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4.23</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="154">
@@ -3967,80 +3967,80 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4.18</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4.02</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4.08</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>US5Y</t>
+          <t>US3Y</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>미국 국채 5년물 (CMT)</t>
+          <t>미국 국채 3년물 (CMT)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="158">
@@ -4059,11 +4059,11 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="159">
@@ -4082,11 +4082,11 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="160">
@@ -4105,11 +4105,11 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4.02</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="161">
@@ -4128,11 +4128,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4.07</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="162">
@@ -4151,11 +4151,11 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="163">
@@ -4174,11 +4174,11 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="164">
@@ -4197,11 +4197,11 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="165">
@@ -4220,11 +4220,11 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="166">
@@ -4243,11 +4243,11 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="167">
@@ -4266,11 +4266,11 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4.32</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="168">
@@ -4289,11 +4289,11 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="169">
@@ -4312,11 +4312,11 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="170">
@@ -4335,11 +4335,11 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="171">
@@ -4358,11 +4358,11 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="172">
@@ -4381,11 +4381,11 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="173">
@@ -4404,11 +4404,11 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4.15</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="174">
@@ -4427,11 +4427,11 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="175">
@@ -4450,11 +4450,11 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="176">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="177">
@@ -4496,11 +4496,11 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="178">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4542,11 +4542,11 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="180">
@@ -4565,11 +4565,11 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4.29</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="181">
@@ -4588,11 +4588,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4.26</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="182">
@@ -4611,11 +4611,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4.27</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="183">
@@ -4634,11 +4634,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4.18</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="184">
@@ -4657,11 +4657,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4.21</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="185">
@@ -4680,11 +4680,11 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4.18</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="186">
@@ -4703,11 +4703,11 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="187">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="188">
@@ -4749,11 +4749,11 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="189">
@@ -4772,11 +4772,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4.29</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="190">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -4818,11 +4818,11 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4.17</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="192">
@@ -4841,11 +4841,11 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4.15</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="193">
@@ -4864,11 +4864,11 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4.12</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="194">
@@ -4887,11 +4887,11 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4.14</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="195">
@@ -4910,11 +4910,11 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4.19</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="196">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4.24</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="197">
@@ -4956,11 +4956,11 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="198">
@@ -4979,11 +4979,11 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="199">
@@ -5002,11 +5002,11 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="200">
@@ -5025,11 +5025,11 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="201">
@@ -5048,11 +5048,11 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4.27</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="202">
@@ -5071,11 +5071,11 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="203">
@@ -5094,11 +5094,11 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="204">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4.31</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="205">
@@ -5140,103 +5140,103 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4.26</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4.2</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4.25</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>US7Y</t>
+          <t>US5Y</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>미국 국채 7년물 (CMT)</t>
+          <t>미국 국채 5년물 (CMT)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4.17</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="210">
@@ -5255,11 +5255,11 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="211">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="212">
@@ -5301,11 +5301,11 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4.24</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="213">
@@ -5324,11 +5324,11 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4.29</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="214">
@@ -5347,11 +5347,11 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="215">
@@ -5370,11 +5370,11 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="216">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4.43</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="217">
@@ -5416,11 +5416,11 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4.43</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="218">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4.5</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="219">
@@ -5462,11 +5462,11 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4.39</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="222">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="223">
@@ -5554,11 +5554,11 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="224">
@@ -5577,11 +5577,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4.29</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="225">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4.27</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="226">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="227">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="228">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4.32</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4.42</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="236">
@@ -5853,11 +5853,11 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="237">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="238">
@@ -5899,11 +5899,11 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4.37</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="239">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4.39</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="241">
@@ -5968,11 +5968,11 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4.38</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="242">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="243">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>4.26</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="244">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4.23</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="245">
@@ -6060,11 +6060,11 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4.24</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="246">
@@ -6083,11 +6083,11 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="247">
@@ -6106,11 +6106,11 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4.35</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="248">
@@ -6129,11 +6129,11 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>4.35</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4.43</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4.42</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="256">
@@ -6313,122 +6313,122 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>US10Y</t>
+          <t>US7Y</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>미국 국채 10년물 (CMT)</t>
+          <t>미국 국채 7년물 (CMT)</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E261" t="n">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4.46</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>4.47</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4.59</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4.67</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="270">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>4.57</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="271">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4.5</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="274">
@@ -6727,11 +6727,11 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4.48</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="275">
@@ -6750,11 +6750,11 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="276">
@@ -6773,11 +6773,11 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="277">
@@ -6796,11 +6796,11 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="278">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4.46</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4.55</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="282">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="283">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>4.53</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="284">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4.55</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4.45</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4.49</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>4.51</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>4.38</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="297">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="298">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>4.49</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>4.48</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="301">
@@ -7348,11 +7348,11 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>4.55</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="302">
@@ -7371,11 +7371,11 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>4.56</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="303">
@@ -7394,11 +7394,11 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="304">
@@ -7417,11 +7417,11 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="305">
@@ -7440,11 +7440,11 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>4.62</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="306">
@@ -7463,11 +7463,11 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="307">
@@ -7486,149 +7486,149 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>3.59</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>3.61</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>3.61</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>3.61</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E312" t="n">
-        <v>3.61</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DTB3</t>
+          <t>US10Y</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>3-Month Treasury Bill</t>
+          <t>미국 국채 10년물 (CMT)</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>3.6</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="314">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="315">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -7716,11 +7716,11 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="318">
@@ -7739,11 +7739,11 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="319">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -7785,11 +7785,11 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="321">
@@ -7808,11 +7808,11 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="322">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="323">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="324">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -7900,11 +7900,11 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E325" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="326">
@@ -7923,11 +7923,11 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="327">
@@ -7946,11 +7946,11 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="328">
@@ -7969,11 +7969,11 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="329">
@@ -7992,11 +7992,11 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="330">
@@ -8015,11 +8015,11 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="331">
@@ -8038,11 +8038,11 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="332">
@@ -8061,11 +8061,11 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="333">
@@ -8084,11 +8084,11 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E333" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="334">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="335">
@@ -8130,11 +8130,11 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="336">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E337" t="n">
@@ -8199,11 +8199,11 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="339">
@@ -8222,11 +8222,11 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="340">
@@ -8245,11 +8245,11 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="341">
@@ -8268,11 +8268,11 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="342">
@@ -8291,11 +8291,11 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="343">
@@ -8314,11 +8314,11 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="344">
@@ -8337,11 +8337,11 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="345">
@@ -8360,11 +8360,11 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="346">
@@ -8383,11 +8383,11 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="347">
@@ -8406,11 +8406,11 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>3.74</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="348">
@@ -8429,11 +8429,11 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="349">
@@ -8452,11 +8452,11 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="350">
@@ -8475,11 +8475,11 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="351">
@@ -8498,11 +8498,11 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>3.74</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="352">
@@ -8521,11 +8521,11 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="353">
@@ -8544,11 +8544,11 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="354">
@@ -8567,11 +8567,11 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>3.69</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="355">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E355" t="n">
@@ -8613,11 +8613,11 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="357">
@@ -8636,11 +8636,11 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="358">
@@ -8659,172 +8659,172 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>3.648</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>3.647</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>3.646</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>3.645</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>3.643</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>3.643</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>SOFR30DAYAVG</t>
+          <t>DTB3</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SOFR 30-Day Average</t>
+          <t>3-Month Treasury Bill</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>3.644</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="366">
@@ -8843,11 +8843,11 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>3.643</v>
+        <v>3.648</v>
       </c>
     </row>
     <row r="367">
@@ -8866,11 +8866,11 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>3.643</v>
+        <v>3.647</v>
       </c>
     </row>
     <row r="368">
@@ -8889,11 +8889,11 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>3.642</v>
+        <v>3.646</v>
       </c>
     </row>
     <row r="369">
@@ -8912,11 +8912,11 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>3.638</v>
+        <v>3.645</v>
       </c>
     </row>
     <row r="370">
@@ -8935,11 +8935,11 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>3.625</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="371">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>3.621</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="372">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>3.616</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="373">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>3.612</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="374">
@@ -9027,11 +9027,11 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>3.608</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="375">
@@ -9050,11 +9050,11 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>3.594</v>
+        <v>3.642</v>
       </c>
     </row>
     <row r="376">
@@ -9073,11 +9073,11 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>3.593</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="377">
@@ -9096,11 +9096,11 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>3.592</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="378">
@@ -9119,11 +9119,11 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>3.592</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="379">
@@ -9142,11 +9142,11 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>3.59</v>
+        <v>3.616</v>
       </c>
     </row>
     <row r="380">
@@ -9165,11 +9165,11 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>3.591</v>
+        <v>3.612</v>
       </c>
     </row>
     <row r="381">
@@ -9188,11 +9188,11 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>3.59</v>
+        <v>3.608</v>
       </c>
     </row>
     <row r="382">
@@ -9211,11 +9211,11 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>3.59</v>
+        <v>3.594</v>
       </c>
     </row>
     <row r="383">
@@ -9234,11 +9234,11 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>3.59</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="384">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E384" t="n">
@@ -9280,11 +9280,11 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>3.593</v>
+        <v>3.592</v>
       </c>
     </row>
     <row r="386">
@@ -9303,11 +9303,11 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="387">
@@ -9326,11 +9326,11 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>3.593</v>
+        <v>3.591</v>
       </c>
     </row>
     <row r="388">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="389">
@@ -9372,11 +9372,11 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>3.601</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="390">
@@ -9395,11 +9395,11 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>3.606</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="391">
@@ -9418,11 +9418,11 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>3.609</v>
+        <v>3.592</v>
       </c>
     </row>
     <row r="392">
@@ -9441,11 +9441,11 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>3.612</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="393">
@@ -9464,11 +9464,11 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E393" t="n">
-        <v>3.626</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="394">
@@ -9487,11 +9487,11 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E394" t="n">
-        <v>3.628</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="395">
@@ -9510,11 +9510,11 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>3.63</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="396">
@@ -9533,11 +9533,11 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>3.632</v>
+        <v>3.601</v>
       </c>
     </row>
     <row r="397">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>3.633</v>
+        <v>3.606</v>
       </c>
     </row>
     <row r="398">
@@ -9579,11 +9579,11 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>3.632</v>
+        <v>3.609</v>
       </c>
     </row>
     <row r="399">
@@ -9602,11 +9602,11 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>3.632</v>
+        <v>3.612</v>
       </c>
     </row>
     <row r="400">
@@ -9625,11 +9625,11 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>3.633</v>
+        <v>3.626</v>
       </c>
     </row>
     <row r="401">
@@ -9648,11 +9648,11 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>3.634</v>
+        <v>3.628</v>
       </c>
     </row>
     <row r="402">
@@ -9671,11 +9671,11 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>3.636</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="403">
@@ -9694,11 +9694,11 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>3.636</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="404">
@@ -9717,11 +9717,11 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>3.636</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="405">
@@ -9740,11 +9740,11 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>3.634</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="406">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E406" t="n">
@@ -9786,11 +9786,11 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>3.625</v>
+        <v>3.633</v>
       </c>
     </row>
     <row r="408">
@@ -9809,11 +9809,11 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>3.624</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="409">
@@ -9832,11 +9832,11 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>3.623</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="410">
@@ -9855,195 +9855,195 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>3.621</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>3.668</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>3.667</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>3.666</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>3.666</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>3.666</v>
+        <v>3.624</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>3.665</v>
+        <v>3.623</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>3.664</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>3.663</v>
+        <v>3.621</v>
       </c>
     </row>
     <row r="419">
@@ -10062,11 +10062,11 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>3.663</v>
+        <v>3.668</v>
       </c>
     </row>
     <row r="420">
@@ -10085,11 +10085,11 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>3.662</v>
+        <v>3.667</v>
       </c>
     </row>
     <row r="421">
@@ -10108,11 +10108,11 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>3.661</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="422">
@@ -10131,11 +10131,11 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>3.657</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="423">
@@ -10154,11 +10154,11 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>3.655</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="424">
@@ -10177,11 +10177,11 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>3.653</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="425">
@@ -10200,11 +10200,11 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>3.651</v>
+        <v>3.664</v>
       </c>
     </row>
     <row r="426">
@@ -10223,11 +10223,11 @@
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>3.649</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="427">
@@ -10246,11 +10246,11 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>3.644</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="428">
@@ -10269,11 +10269,11 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>3.644</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="429">
@@ -10292,11 +10292,11 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>3.643</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="430">
@@ -10315,11 +10315,11 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>3.643</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="431">
@@ -10338,11 +10338,11 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>3.641</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="432">
@@ -10361,11 +10361,11 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>3.64</v>
+        <v>3.653</v>
       </c>
     </row>
     <row r="433">
@@ -10384,11 +10384,11 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>3.64</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="434">
@@ -10407,11 +10407,11 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>3.639</v>
+        <v>3.649</v>
       </c>
     </row>
     <row r="435">
@@ -10430,11 +10430,11 @@
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>3.639</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="436">
@@ -10453,11 +10453,11 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>3.638</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="437">
@@ -10476,11 +10476,11 @@
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>3.638</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="438">
@@ -10499,11 +10499,11 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>3.637</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="439">
@@ -10522,11 +10522,11 @@
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E439" t="n">
-        <v>3.637</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="440">
@@ -10545,11 +10545,11 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>3.636</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="441">
@@ -10568,11 +10568,11 @@
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>3.636</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="442">
@@ -10591,11 +10591,11 @@
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E442" t="n">
-        <v>3.636</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="443">
@@ -10614,11 +10614,11 @@
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E443" t="n">
-        <v>3.636</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="444">
@@ -10637,11 +10637,11 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E444" t="n">
-        <v>3.636</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="445">
@@ -10660,11 +10660,11 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E445" t="n">
-        <v>3.636</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="446">
@@ -10683,11 +10683,11 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E446" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="447">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E447" t="n">
-        <v>3.636</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="448">
@@ -10729,11 +10729,11 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E448" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="449">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -10775,11 +10775,11 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E450" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="451">
@@ -10798,11 +10798,11 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E451" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="452">
@@ -10821,11 +10821,11 @@
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E452" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="453">
@@ -10844,11 +10844,11 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E453" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="454">
@@ -10867,11 +10867,11 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E454" t="n">
-        <v>3.634</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="455">
@@ -10890,11 +10890,11 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E455" t="n">
-        <v>3.634</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="456">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E456" t="n">
@@ -10936,11 +10936,11 @@
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E457" t="n">
-        <v>3.635</v>
+        <v>3.636</v>
       </c>
     </row>
     <row r="458">
@@ -10959,11 +10959,11 @@
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E458" t="n">
-        <v>3.634</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="459">
@@ -10982,11 +10982,11 @@
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E459" t="n">
-        <v>3.632</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="460">
@@ -11005,11 +11005,11 @@
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E460" t="n">
-        <v>3.631</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="461">
@@ -11028,11 +11028,11 @@
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E461" t="n">
-        <v>3.63</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="462">
@@ -11051,218 +11051,218 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E462" t="n">
-        <v>3.63</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E463" t="n">
-        <v>1.24161826</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E464" t="n">
-        <v>1.24199489</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E465" t="n">
-        <v>1.24212012</v>
+        <v>3.635</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E466" t="n">
-        <v>1.24224503</v>
+        <v>3.634</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E467" t="n">
-        <v>1.2423696</v>
+        <v>3.632</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E468" t="n">
-        <v>1.24249383</v>
+        <v>3.631</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E469" t="n">
-        <v>1.24286658</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E470" t="n">
-        <v>1.24299087</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E471" t="n">
-        <v>1.24311517</v>
+        <v>3.629</v>
       </c>
     </row>
     <row r="472">
@@ -11281,11 +11281,11 @@
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E472" t="n">
-        <v>1.24323913</v>
+        <v>1.24161826</v>
       </c>
     </row>
     <row r="473">
@@ -11304,11 +11304,11 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E473" t="n">
-        <v>1.24336207</v>
+        <v>1.24199489</v>
       </c>
     </row>
     <row r="474">
@@ -11327,11 +11327,11 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E474" t="n">
-        <v>1.2437299</v>
+        <v>1.24212012</v>
       </c>
     </row>
     <row r="475">
@@ -11350,11 +11350,11 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E475" t="n">
-        <v>1.24385186</v>
+        <v>1.24224503</v>
       </c>
     </row>
     <row r="476">
@@ -11373,11 +11373,11 @@
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E476" t="n">
-        <v>1.24397313</v>
+        <v>1.2423696</v>
       </c>
     </row>
     <row r="477">
@@ -11396,11 +11396,11 @@
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E477" t="n">
-        <v>1.24409407</v>
+        <v>1.24249383</v>
       </c>
     </row>
     <row r="478">
@@ -11419,11 +11419,11 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E478" t="n">
-        <v>1.24421537</v>
+        <v>1.24286658</v>
       </c>
     </row>
     <row r="479">
@@ -11442,11 +11442,11 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E479" t="n">
-        <v>1.24470615</v>
+        <v>1.24299087</v>
       </c>
     </row>
     <row r="480">
@@ -11465,11 +11465,11 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E480" t="n">
-        <v>1.24483166</v>
+        <v>1.24311517</v>
       </c>
     </row>
     <row r="481">
@@ -11488,11 +11488,11 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E481" t="n">
-        <v>1.24495718</v>
+        <v>1.24323913</v>
       </c>
     </row>
     <row r="482">
@@ -11511,11 +11511,11 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E482" t="n">
-        <v>1.24508236</v>
+        <v>1.24336207</v>
       </c>
     </row>
     <row r="483">
@@ -11534,11 +11534,11 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E483" t="n">
-        <v>1.245459</v>
+        <v>1.2437299</v>
       </c>
     </row>
     <row r="484">
@@ -11557,11 +11557,11 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E484" t="n">
-        <v>1.24558528</v>
+        <v>1.24385186</v>
       </c>
     </row>
     <row r="485">
@@ -11580,11 +11580,11 @@
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E485" t="n">
-        <v>1.24571087</v>
+        <v>1.24397313</v>
       </c>
     </row>
     <row r="486">
@@ -11603,11 +11603,11 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E486" t="n">
-        <v>1.24583579</v>
+        <v>1.24409407</v>
       </c>
     </row>
     <row r="487">
@@ -11626,11 +11626,11 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E487" t="n">
-        <v>1.24596107</v>
+        <v>1.24421537</v>
       </c>
     </row>
     <row r="488">
@@ -11649,11 +11649,11 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E488" t="n">
-        <v>1.24633797</v>
+        <v>1.24470615</v>
       </c>
     </row>
     <row r="489">
@@ -11672,11 +11672,11 @@
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E489" t="n">
-        <v>1.24646364</v>
+        <v>1.24483166</v>
       </c>
     </row>
     <row r="490">
@@ -11695,11 +11695,11 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E490" t="n">
-        <v>1.24658829</v>
+        <v>1.24495718</v>
       </c>
     </row>
     <row r="491">
@@ -11718,11 +11718,11 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E491" t="n">
-        <v>1.2467126</v>
+        <v>1.24508236</v>
       </c>
     </row>
     <row r="492">
@@ -11741,11 +11741,11 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E492" t="n">
-        <v>1.24683727</v>
+        <v>1.245459</v>
       </c>
     </row>
     <row r="493">
@@ -11764,11 +11764,11 @@
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E493" t="n">
-        <v>1.24721652</v>
+        <v>1.24558528</v>
       </c>
     </row>
     <row r="494">
@@ -11787,11 +11787,11 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E494" t="n">
-        <v>1.24734436</v>
+        <v>1.24571087</v>
       </c>
     </row>
     <row r="495">
@@ -11810,11 +11810,11 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E495" t="n">
-        <v>1.24747013</v>
+        <v>1.24583579</v>
       </c>
     </row>
     <row r="496">
@@ -11833,11 +11833,11 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E496" t="n">
-        <v>1.24759592</v>
+        <v>1.24596107</v>
       </c>
     </row>
     <row r="497">
@@ -11856,11 +11856,11 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E497" t="n">
-        <v>1.24809773</v>
+        <v>1.24633797</v>
       </c>
     </row>
     <row r="498">
@@ -11879,11 +11879,11 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E498" t="n">
-        <v>1.24822289</v>
+        <v>1.24646364</v>
       </c>
     </row>
     <row r="499">
@@ -11902,11 +11902,11 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E499" t="n">
-        <v>1.2483484</v>
+        <v>1.24658829</v>
       </c>
     </row>
     <row r="500">
@@ -11925,11 +11925,11 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E500" t="n">
-        <v>1.24847393</v>
+        <v>1.2467126</v>
       </c>
     </row>
     <row r="501">
@@ -11948,11 +11948,11 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E501" t="n">
-        <v>1.24860016</v>
+        <v>1.24683727</v>
       </c>
     </row>
     <row r="502">
@@ -11971,11 +11971,11 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E502" t="n">
-        <v>1.24897683</v>
+        <v>1.24721652</v>
       </c>
     </row>
     <row r="503">
@@ -11994,11 +11994,11 @@
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E503" t="n">
-        <v>1.24910242</v>
+        <v>1.24734436</v>
       </c>
     </row>
     <row r="504">
@@ -12017,11 +12017,11 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E504" t="n">
-        <v>1.2492301</v>
+        <v>1.24747013</v>
       </c>
     </row>
     <row r="505">
@@ -12040,11 +12040,11 @@
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E505" t="n">
-        <v>1.24935711</v>
+        <v>1.24759592</v>
       </c>
     </row>
     <row r="506">
@@ -12063,11 +12063,11 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E506" t="n">
-        <v>1.2498624</v>
+        <v>1.24809773</v>
       </c>
     </row>
     <row r="507">
@@ -12086,11 +12086,11 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E507" t="n">
-        <v>1.24998843</v>
+        <v>1.24822289</v>
       </c>
     </row>
     <row r="508">
@@ -12109,11 +12109,11 @@
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E508" t="n">
-        <v>1.25011412</v>
+        <v>1.2483484</v>
       </c>
     </row>
     <row r="509">
@@ -12132,11 +12132,11 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E509" t="n">
-        <v>1.25023844</v>
+        <v>1.24847393</v>
       </c>
     </row>
     <row r="510">
@@ -12155,11 +12155,11 @@
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E510" t="n">
-        <v>1.25036103</v>
+        <v>1.24860016</v>
       </c>
     </row>
     <row r="511">
@@ -12178,11 +12178,11 @@
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E511" t="n">
-        <v>1.25073093</v>
+        <v>1.24897683</v>
       </c>
     </row>
     <row r="512">
@@ -12201,11 +12201,11 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E512" t="n">
-        <v>1.25085601</v>
+        <v>1.24910242</v>
       </c>
     </row>
     <row r="513">
@@ -12224,11 +12224,11 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E513" t="n">
-        <v>1.25098213</v>
+        <v>1.2492301</v>
       </c>
     </row>
     <row r="514">
@@ -12247,241 +12247,241 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E514" t="n">
-        <v>1.25110862</v>
+        <v>1.24935711</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E515" t="n">
-        <v>4.97</v>
+        <v>1.2498624</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E516" t="n">
-        <v>5.02</v>
+        <v>1.24998843</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E517" t="n">
-        <v>4.98</v>
+        <v>1.25011412</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E518" t="n">
-        <v>4.94</v>
+        <v>1.25023844</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E519" t="n">
-        <v>4.97</v>
+        <v>1.25036103</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E520" t="n">
-        <v>4.95</v>
+        <v>1.25073093</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E521" t="n">
-        <v>4.98</v>
+        <v>1.25085601</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E522" t="n">
-        <v>5.03</v>
+        <v>1.25098213</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E523" t="n">
-        <v>5.03</v>
+        <v>1.25110862</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260717</t>
         </is>
       </c>
       <c r="E524" t="n">
-        <v>5.02</v>
+        <v>1.25123443</v>
       </c>
     </row>
     <row r="525">
@@ -12500,11 +12500,11 @@
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E525" t="n">
-        <v>5.12</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="526">
@@ -12523,11 +12523,11 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E526" t="n">
-        <v>5.14</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="527">
@@ -12546,11 +12546,11 @@
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E527" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="528">
@@ -12569,11 +12569,11 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E528" t="n">
-        <v>5.11</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="529">
@@ -12592,11 +12592,11 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E529" t="n">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="530">
@@ -12615,11 +12615,11 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E530" t="n">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="531">
@@ -12638,11 +12638,11 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E531" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="532">
@@ -12661,11 +12661,11 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E532" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="533">
@@ -12684,11 +12684,11 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E533" t="n">
-        <v>4.98</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="534">
@@ -12707,11 +12707,11 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E534" t="n">
-        <v>4.99</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="535">
@@ -12730,11 +12730,11 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E535" t="n">
-        <v>4.99</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="536">
@@ -12753,11 +12753,11 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E536" t="n">
-        <v>4.97</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="537">
@@ -12776,11 +12776,11 @@
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E537" t="n">
-        <v>4.99</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="538">
@@ -12799,11 +12799,11 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>4.97</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="539">
@@ -12822,11 +12822,11 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="540">
@@ -12845,11 +12845,11 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="541">
@@ -12868,11 +12868,11 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>5.01</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="542">
@@ -12891,11 +12891,11 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="543">
@@ -12914,11 +12914,11 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="544">
@@ -12937,11 +12937,11 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="545">
@@ -12960,11 +12960,11 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="546">
@@ -12983,11 +12983,11 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="547">
@@ -13006,11 +13006,11 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>4.93</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="548">
@@ -13029,11 +13029,11 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="549">
@@ -13052,11 +13052,11 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>4.95</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="550">
@@ -13075,11 +13075,11 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>4.94</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="551">
@@ -13098,11 +13098,11 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>4.86</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="552">
@@ -13121,11 +13121,11 @@
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E552" t="n">
-        <v>4.86</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="553">
@@ -13144,11 +13144,11 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>4.87</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="554">
@@ -13167,11 +13167,11 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E554" t="n">
-        <v>4.86</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="555">
@@ -13190,11 +13190,11 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="556">
@@ -13213,11 +13213,11 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>4.97</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="557">
@@ -13236,11 +13236,11 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>4.98</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="558">
@@ -13259,11 +13259,11 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="559">
@@ -13282,11 +13282,11 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="560">
@@ -13305,11 +13305,11 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>5.06</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="561">
@@ -13328,11 +13328,11 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>5.05</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="562">
@@ -13351,11 +13351,11 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>5.06</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="563">
@@ -13374,11 +13374,11 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>5.1</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="564">
@@ -13397,11 +13397,11 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E564" t="n">
-        <v>5.08</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="565">
@@ -13420,264 +13420,264 @@
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E565" t="n">
-        <v>5.08</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E566" t="n">
-        <v>1.91</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E567" t="n">
-        <v>1.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E568" t="n">
-        <v>1.96</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E569" t="n">
-        <v>1.94</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E570" t="n">
-        <v>1.96</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E571" t="n">
-        <v>1.93</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E572" t="n">
-        <v>1.95</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E573" t="n">
-        <v>1.99</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E574" t="n">
-        <v>1.99</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E575" t="n">
-        <v>2</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>US10Y_TIPS</t>
+          <t>US30Y</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>미국 10년 실질금리 (TIPS)</t>
+          <t>미국 국채 30년물 (CMT)</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E576" t="n">
-        <v>2.1</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="577">
@@ -13696,11 +13696,11 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E577" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="578">
@@ -13719,11 +13719,11 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E578" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="579">
@@ -13742,11 +13742,11 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="580">
@@ -13765,11 +13765,11 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="581">
@@ -13788,11 +13788,11 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="582">
@@ -13811,11 +13811,11 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="583">
@@ -13834,11 +13834,11 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="584">
@@ -13857,11 +13857,11 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="585">
@@ -13880,11 +13880,11 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="586">
@@ -13903,11 +13903,11 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
     </row>
     <row r="587">
@@ -13926,11 +13926,11 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="588">
@@ -13949,11 +13949,11 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="589">
@@ -13972,11 +13972,11 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="590">
@@ -13995,11 +13995,11 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="591">
@@ -14018,11 +14018,11 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="592">
@@ -14041,11 +14041,11 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="593">
@@ -14064,11 +14064,11 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="594">
@@ -14087,11 +14087,11 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="595">
@@ -14110,11 +14110,11 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="596">
@@ -14133,11 +14133,11 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="597">
@@ -14156,11 +14156,11 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="598">
@@ -14179,11 +14179,11 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="599">
@@ -14202,11 +14202,11 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="600">
@@ -14225,11 +14225,11 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="601">
@@ -14248,11 +14248,11 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="602">
@@ -14271,11 +14271,11 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="603">
@@ -14294,11 +14294,11 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="604">
@@ -14317,11 +14317,11 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="605">
@@ -14340,7 +14340,7 @@
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E605" t="n">
@@ -14363,11 +14363,11 @@
       </c>
       <c r="D606" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E606" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="607">
@@ -14386,11 +14386,11 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E607" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="608">
@@ -14409,11 +14409,11 @@
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E608" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="609">
@@ -14432,11 +14432,11 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E609" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="610">
@@ -14455,11 +14455,11 @@
       </c>
       <c r="D610" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E610" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="611">
@@ -14478,11 +14478,11 @@
       </c>
       <c r="D611" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E611" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="612">
@@ -14501,11 +14501,11 @@
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E612" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="613">
@@ -14524,11 +14524,11 @@
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="614">
@@ -14547,11 +14547,11 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="615">
@@ -14570,11 +14570,11 @@
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E615" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="616">
@@ -14593,287 +14593,287 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E616" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260630</t>
         </is>
       </c>
       <c r="E617" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260701</t>
         </is>
       </c>
       <c r="E618" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260702</t>
         </is>
       </c>
       <c r="E619" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260706</t>
         </is>
       </c>
       <c r="E620" t="n">
-        <v>2.42</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260707</t>
         </is>
       </c>
       <c r="E621" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260708</t>
         </is>
       </c>
       <c r="E622" t="n">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260709</t>
         </is>
       </c>
       <c r="E623" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260710</t>
         </is>
       </c>
       <c r="E624" t="n">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260713</t>
         </is>
       </c>
       <c r="E625" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260714</t>
         </is>
       </c>
       <c r="E626" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260715</t>
         </is>
       </c>
       <c r="E627" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>US10Y_BEI</t>
+          <t>US10Y_TIPS</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>미국 10년 기대인플레 (BEI)</t>
+          <t>미국 10년 실질금리 (TIPS)</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260716</t>
         </is>
       </c>
       <c r="E628" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="629">
@@ -14892,11 +14892,11 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E629" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="630">
@@ -14915,11 +14915,11 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E630" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="631">
@@ -14938,11 +14938,11 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="632">
@@ -14961,11 +14961,11 @@
       </c>
       <c r="D632" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E632" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="633">
@@ -14984,11 +14984,11 @@
       </c>
       <c r="D633" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E633" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="634">
@@ -15007,11 +15007,11 @@
       </c>
       <c r="D634" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E634" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="635">
@@ -15030,11 +15030,11 @@
       </c>
       <c r="D635" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E635" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="636">
@@ -15053,11 +15053,11 @@
       </c>
       <c r="D636" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E636" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="637">
@@ -15076,11 +15076,11 @@
       </c>
       <c r="D637" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E637" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="638">
@@ -15099,11 +15099,11 @@
       </c>
       <c r="D638" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E638" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="639">
@@ -15122,11 +15122,11 @@
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E639" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="640">
@@ -15145,11 +15145,11 @@
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E640" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="641">
@@ -15168,11 +15168,11 @@
       </c>
       <c r="D641" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E641" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="642">
@@ -15191,11 +15191,11 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E642" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="643">
@@ -15214,11 +15214,11 @@
       </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E643" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="644">
@@ -15237,11 +15237,11 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E644" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="645">
@@ -15260,11 +15260,11 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>20260611</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E645" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="646">
@@ -15283,11 +15283,11 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>20260612</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="647">
@@ -15306,11 +15306,11 @@
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>20260615</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="648">
@@ -15329,11 +15329,11 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>20260616</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E648" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="649">
@@ -15352,11 +15352,11 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>20260617</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E649" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="650">
@@ -15375,11 +15375,11 @@
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>20260618</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="651">
@@ -15398,11 +15398,11 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>20260622</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="652">
@@ -15421,11 +15421,11 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>20260623</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>2.21</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="653">
@@ -15444,11 +15444,11 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>20260624</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E653" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="654">
@@ -15467,11 +15467,11 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>20260625</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E654" t="n">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="655">
@@ -15490,11 +15490,11 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>20260626</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E655" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="656">
@@ -15513,11 +15513,11 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>20260629</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E656" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="657">
@@ -15536,11 +15536,11 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>20260630</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E657" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="658">
@@ -15559,11 +15559,11 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>20260701</t>
+          <t>20260612</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="659">
@@ -15582,11 +15582,11 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>20260702</t>
+          <t>20260615</t>
         </is>
       </c>
       <c r="E659" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="660">
@@ -15605,11 +15605,11 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>20260706</t>
+          <t>20260616</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="661">
@@ -15628,11 +15628,11 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>20260707</t>
+          <t>20260617</t>
         </is>
       </c>
       <c r="E661" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="662">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>20260708</t>
+          <t>20260618</t>
         </is>
       </c>
       <c r="E662" t="n">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>20260709</t>
+          <t>20260622</t>
         </is>
       </c>
       <c r="E663" t="n">
@@ -15697,11 +15697,11 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>20260710</t>
+          <t>20260623</t>
         </is>
       </c>
       <c r="E664" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="665">
@@ -15720,11 +15720,11 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>20260713</t>
+          <t>20260624</t>
         </is>
       </c>
       <c r="E665" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="666">
@@ -15743,11 +15743,11 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>20260714</t>
+          <t>20260625</t>
         </is>
       </c>
       <c r="E666" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="667">
@@ -15766,11 +15766,11 @@
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>20260715</t>
+          <t>20260626</t>
         </is>
       </c>
       <c r="E667" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="668">
@@ -15789,11 +15789,310 @@
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>20260716</t>
+          <t>20260629</t>
         </is>
       </c>
       <c r="E668" t="n">
         <v>2.22</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="n">
+        <v>15</v>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>20260630</t>
+        </is>
+      </c>
+      <c r="E669" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="n">
+        <v>15</v>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>20260701</t>
+        </is>
+      </c>
+      <c r="E670" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="n">
+        <v>15</v>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>20260702</t>
+        </is>
+      </c>
+      <c r="E671" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="n">
+        <v>15</v>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>20260706</t>
+        </is>
+      </c>
+      <c r="E672" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="n">
+        <v>15</v>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>20260707</t>
+        </is>
+      </c>
+      <c r="E673" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="n">
+        <v>15</v>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>20260708</t>
+        </is>
+      </c>
+      <c r="E674" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="n">
+        <v>15</v>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>20260709</t>
+        </is>
+      </c>
+      <c r="E675" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="n">
+        <v>15</v>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>20260710</t>
+        </is>
+      </c>
+      <c r="E676" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="n">
+        <v>15</v>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>20260713</t>
+        </is>
+      </c>
+      <c r="E677" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="n">
+        <v>15</v>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>20260714</t>
+        </is>
+      </c>
+      <c r="E678" t="n">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>15</v>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>20260715</t>
+        </is>
+      </c>
+      <c r="E679" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="n">
+        <v>15</v>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>20260716</t>
+        </is>
+      </c>
+      <c r="E680" t="n">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="n">
+        <v>15</v>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>US10Y_BEI</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>미국 10년 기대인플레 (BEI)</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>20260717</t>
+        </is>
+      </c>
+      <c r="E681" t="n">
+        <v>2.24</v>
       </c>
     </row>
   </sheetData>
